--- a/TimeCardCore/wwwroot/content/bigrockTemplate.xlsx
+++ b/TimeCardCore/wwwroot/content/bigrockTemplate.xlsx
@@ -1,24 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gcorr\source\repos\TimeCardCore\TimeCardCore\wwwroot\content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7055A1FF-DBF4-4114-BD82-F34A69AB2F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31548D41-18A9-4718-B53B-B98C8257D16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="14640" windowWidth="29040" windowHeight="16440" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C1 W1" sheetId="20" r:id="rId1"/>
     <sheet name="C1 W2" sheetId="24" r:id="rId2"/>
+    <sheet name="C1 W3" sheetId="25" r:id="rId3"/>
+    <sheet name="C1 W4" sheetId="26" r:id="rId4"/>
+    <sheet name="C1 W5" sheetId="27" r:id="rId5"/>
+    <sheet name="C1 W6" sheetId="28" r:id="rId6"/>
+    <sheet name="C1 W7" sheetId="29" r:id="rId7"/>
+    <sheet name="C1 W8" sheetId="30" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'C1 W1'!$A$1:$O$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'C1 W2'!$A$1:$O$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'C1 W3'!$A$1:$O$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'C1 W4'!$A$1:$O$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'C1 W5'!$A$1:$O$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'C1 W6'!$A$1:$O$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'C1 W7'!$A$1:$O$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'C1 W8'!$A$1:$O$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="29">
   <si>
     <t>Client Name</t>
   </si>
@@ -690,6 +702,34 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -699,6 +739,26 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -1370,6 +1430,2010 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>9525</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19457" name="Picture 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s19457"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3F41A5B-9EA1-45B3-88C1-8205DCEF73AF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>361950</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>657225</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19458" name="Check Box 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s19458"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E54EBCCC-172B-4D2E-90FA-8DE2D7F4A1D1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>361950</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>200025</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>657225</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>200025</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19459" name="Check Box 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s19459"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47B1E13C-1BD3-4D92-A0B7-CC4F3530096D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>9525</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19460" name="Picture 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s19460"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82A8C142-7B9D-4BD3-B0CD-80BC573B8821}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5086350</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>278179</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{131AB0EC-5CDB-4C71-8D46-0EDE4F506BD4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="114300" y="219075"/>
+          <a:ext cx="5086350" cy="278179"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>9525</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="20481" name="Picture 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s20481"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11DF9B7E-E0A8-43C6-8C8C-C67FDD75771E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>361950</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>657225</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="20482" name="Check Box 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s20482"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63131000-C945-4966-AE06-DAA2C78406A2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>361950</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>200025</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>657225</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>200025</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="20483" name="Check Box 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s20483"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57B11B1D-EB8A-41D5-B164-7246A0A0E4C8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>9525</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="20484" name="Picture 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s20484"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E3D5C74-343A-48BF-9C81-D17FDD9E50CB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5086350</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>278179</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{647DCED0-DCCB-424C-94E2-901C53A9C40C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="114300" y="219075"/>
+          <a:ext cx="5086350" cy="278179"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>9525</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="21505" name="Picture 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s21505"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F221732C-7C59-41DB-A533-471066658DEB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>361950</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>657225</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="21506" name="Check Box 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s21506"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDB8A8FF-1382-47A5-A6F0-66D93C6A06B2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>361950</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>200025</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>657225</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>200025</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="21507" name="Check Box 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s21507"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{955D170A-2A17-4C09-BBD9-C445643957C0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>9525</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="21508" name="Picture 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s21508"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D00172E-B96E-4F40-AD51-93FAC652DFD5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5086350</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>278179</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{815F6124-BD08-49B9-854E-A1F29E5AC10C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="114300" y="219075"/>
+          <a:ext cx="5086350" cy="278179"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>9525</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22529" name="Picture 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s22529"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C84AAFAA-9F47-4D5E-92AB-DFF90361961D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>361950</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>657225</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22530" name="Check Box 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s22530"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34DCB5A3-1B0A-4B49-9734-F2B091D9DFDC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>361950</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>200025</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>657225</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>200025</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22531" name="Check Box 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s22531"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15918071-543E-4B13-8477-FD3BA892A464}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>9525</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22532" name="Picture 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s22532"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0E42699-FB26-4EA4-A99D-60F3E84F2878}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5086350</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>278179</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7F137C6-5C0B-4FB5-930F-62B7918A7FDC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="114300" y="219075"/>
+          <a:ext cx="5086350" cy="278179"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>9525</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="23553" name="Picture 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s23553"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5440B8D-5DFC-4FAD-95BA-C53C8252BC05}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>361950</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>657225</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="23554" name="Check Box 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s23554"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC14730E-AF69-4228-9842-AF7DF3A74C9C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>361950</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>200025</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>657225</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>200025</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="23555" name="Check Box 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s23555"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F4B02F5-B66D-42F5-B046-1297559911F9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>9525</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="23556" name="Picture 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s23556"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD83A688-6BDF-4889-BC72-86EB8427C383}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5086350</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>278179</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9A9B968-306B-4A55-9090-95A27D687C84}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="114300" y="219075"/>
+          <a:ext cx="5086350" cy="278179"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>9525</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="24577" name="Picture 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s24577"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7B27E53-A888-4F88-A184-DDDFC9B3063E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>361950</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>657225</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="24578" name="Check Box 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s24578"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFB10983-82FD-4508-BBBE-E7900E84D8E2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>361950</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>200025</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>12</xdr:col>
+          <xdr:colOff>657225</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>200025</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="24579" name="Check Box 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s24579"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24439C8C-3A3E-4239-BEC2-5B4CC653722A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>9525</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="24580" name="Picture 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s24580"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{093AAAC9-D9F6-49E7-9EBA-ECF2D1B72092}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData fLocksWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5086350</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>278179</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0C37819-F399-4B29-83C3-F615983C43F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="114300" y="219075"/>
+          <a:ext cx="5086350" cy="278179"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2149,7 +4213,7 @@
       <c r="K19" s="26"/>
       <c r="L19" s="73">
         <f ca="1">NOW()</f>
-        <v>46215.307118287034</v>
+        <v>46305.419900115739</v>
       </c>
       <c r="M19" s="74"/>
     </row>
@@ -2746,7 +4810,7 @@
       <c r="K19" s="26"/>
       <c r="L19" s="73">
         <f ca="1">NOW()</f>
-        <v>46215.307118287034</v>
+        <v>46305.419900115739</v>
       </c>
       <c r="M19" s="74"/>
     </row>
@@ -2930,4 +4994,3580 @@
     </mc:Choice>
   </mc:AlternateContent>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF9C4ED5-75F2-4C01-A9D6-502F96E69EA9}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R24"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" customWidth="1"/>
+    <col min="2" max="2" width="81.28515625" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="58"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="75" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+    </row>
+    <row r="2" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="75"/>
+    </row>
+    <row r="3" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="57"/>
+      <c r="B3" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="57"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+    </row>
+    <row r="4" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="57"/>
+      <c r="B4" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+    </row>
+    <row r="5" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="57"/>
+      <c r="B5" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+    </row>
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L7" s="5"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="8"/>
+    </row>
+    <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="77"/>
+      <c r="I8" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="79"/>
+      <c r="K8" s="13">
+        <f>'C1 W1'!K8+7</f>
+        <v>46214</v>
+      </c>
+      <c r="L8" s="14"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="17"/>
+    </row>
+    <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="48">
+        <f t="shared" ref="G10:M10" si="0">G11</f>
+        <v>46208</v>
+      </c>
+      <c r="H10" s="48">
+        <f t="shared" si="0"/>
+        <v>46209</v>
+      </c>
+      <c r="I10" s="48">
+        <f t="shared" si="0"/>
+        <v>46210</v>
+      </c>
+      <c r="J10" s="48">
+        <f t="shared" si="0"/>
+        <v>46211</v>
+      </c>
+      <c r="K10" s="48">
+        <f t="shared" si="0"/>
+        <v>46212</v>
+      </c>
+      <c r="L10" s="48">
+        <f t="shared" si="0"/>
+        <v>46213</v>
+      </c>
+      <c r="M10" s="48">
+        <f t="shared" si="0"/>
+        <v>46214</v>
+      </c>
+      <c r="N10" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="O10" s="33"/>
+    </row>
+    <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="37"/>
+      <c r="B11" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="49">
+        <f t="shared" ref="G11:L11" si="1">H11-1</f>
+        <v>46208</v>
+      </c>
+      <c r="H11" s="49">
+        <f t="shared" si="1"/>
+        <v>46209</v>
+      </c>
+      <c r="I11" s="49">
+        <f t="shared" si="1"/>
+        <v>46210</v>
+      </c>
+      <c r="J11" s="49">
+        <f t="shared" si="1"/>
+        <v>46211</v>
+      </c>
+      <c r="K11" s="49">
+        <f t="shared" si="1"/>
+        <v>46212</v>
+      </c>
+      <c r="L11" s="49">
+        <f t="shared" si="1"/>
+        <v>46213</v>
+      </c>
+      <c r="M11" s="49">
+        <f>K8</f>
+        <v>46214</v>
+      </c>
+      <c r="N11" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="42"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+    </row>
+    <row r="13" spans="1:18" ht="0.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="54"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="55"/>
+    </row>
+    <row r="14" spans="1:18" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="47"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="69">
+        <f>SUM(G14:M14)</f>
+        <v>0</v>
+      </c>
+      <c r="R14"/>
+    </row>
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="30"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+    </row>
+    <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="40"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="41">
+        <f t="shared" ref="G16:O16" si="2">SUM(G14:G15)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="38">
+        <f>SUM(N16:O16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L18" s="24"/>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="25"/>
+      <c r="B19" s="34"/>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="26"/>
+      <c r="L19" s="73">
+        <f ca="1">NOW()</f>
+        <v>46305.419900115739</v>
+      </c>
+      <c r="M19" s="74"/>
+    </row>
+    <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L20" s="24"/>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="25"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="28"/>
+    </row>
+    <row r="22" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" s="22"/>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="28"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="M1:O4"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="L19:M19"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.14000000000000001" right="0.12" top="0.54" bottom="0.47" header="0.5" footer="0.38"/>
+  <pageSetup scale="91" orientation="landscape" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <oleObjects>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Wordpad.Document.1" shapeId="19457" r:id="rId4">
+          <objectPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId5">
+            <anchor moveWithCells="1" sizeWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Wordpad.Document.1" shapeId="19457" r:id="rId4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Wordpad.Document.1" shapeId="19460" r:id="rId6">
+          <objectPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId5">
+            <anchor moveWithCells="1" sizeWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Wordpad.Document.1" shapeId="19460" r:id="rId6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </oleObjects>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="19458" r:id="rId7" name="Check Box 2">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>361950</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>657225</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="19459" r:id="rId8" name="Check Box 3">
+              <controlPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>361950</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>200025</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>657225</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>200025</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F991817-C06C-40D6-A013-9AF509F2BBEA}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R24"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" customWidth="1"/>
+    <col min="2" max="2" width="81.28515625" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="58"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="75" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+    </row>
+    <row r="2" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="75"/>
+    </row>
+    <row r="3" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="57"/>
+      <c r="B3" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="57"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+    </row>
+    <row r="4" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="57"/>
+      <c r="B4" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+    </row>
+    <row r="5" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="57"/>
+      <c r="B5" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+    </row>
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L7" s="5"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="8"/>
+    </row>
+    <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="77"/>
+      <c r="I8" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="79"/>
+      <c r="K8" s="13">
+        <f>'C1 W1'!K8+7</f>
+        <v>46214</v>
+      </c>
+      <c r="L8" s="14"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="17"/>
+    </row>
+    <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="48">
+        <f t="shared" ref="G10:M10" si="0">G11</f>
+        <v>46208</v>
+      </c>
+      <c r="H10" s="48">
+        <f t="shared" si="0"/>
+        <v>46209</v>
+      </c>
+      <c r="I10" s="48">
+        <f t="shared" si="0"/>
+        <v>46210</v>
+      </c>
+      <c r="J10" s="48">
+        <f t="shared" si="0"/>
+        <v>46211</v>
+      </c>
+      <c r="K10" s="48">
+        <f t="shared" si="0"/>
+        <v>46212</v>
+      </c>
+      <c r="L10" s="48">
+        <f t="shared" si="0"/>
+        <v>46213</v>
+      </c>
+      <c r="M10" s="48">
+        <f t="shared" si="0"/>
+        <v>46214</v>
+      </c>
+      <c r="N10" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="O10" s="33"/>
+    </row>
+    <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="37"/>
+      <c r="B11" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="49">
+        <f t="shared" ref="G11:L11" si="1">H11-1</f>
+        <v>46208</v>
+      </c>
+      <c r="H11" s="49">
+        <f t="shared" si="1"/>
+        <v>46209</v>
+      </c>
+      <c r="I11" s="49">
+        <f t="shared" si="1"/>
+        <v>46210</v>
+      </c>
+      <c r="J11" s="49">
+        <f t="shared" si="1"/>
+        <v>46211</v>
+      </c>
+      <c r="K11" s="49">
+        <f t="shared" si="1"/>
+        <v>46212</v>
+      </c>
+      <c r="L11" s="49">
+        <f t="shared" si="1"/>
+        <v>46213</v>
+      </c>
+      <c r="M11" s="49">
+        <f>K8</f>
+        <v>46214</v>
+      </c>
+      <c r="N11" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="42"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+    </row>
+    <row r="13" spans="1:18" ht="0.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="54"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="55"/>
+    </row>
+    <row r="14" spans="1:18" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="47"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="69">
+        <f>SUM(G14:M14)</f>
+        <v>0</v>
+      </c>
+      <c r="R14"/>
+    </row>
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="30"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+    </row>
+    <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="40"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="41">
+        <f t="shared" ref="G16:O16" si="2">SUM(G14:G15)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="38">
+        <f>SUM(N16:O16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L18" s="24"/>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="25"/>
+      <c r="B19" s="34"/>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="26"/>
+      <c r="L19" s="73">
+        <f ca="1">NOW()</f>
+        <v>46305.419900115739</v>
+      </c>
+      <c r="M19" s="74"/>
+    </row>
+    <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L20" s="24"/>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="25"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="28"/>
+    </row>
+    <row r="22" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" s="22"/>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="28"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="M1:O4"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="L19:M19"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.14000000000000001" right="0.12" top="0.54" bottom="0.47" header="0.5" footer="0.38"/>
+  <pageSetup scale="91" orientation="landscape" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <oleObjects>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Wordpad.Document.1" shapeId="20481" r:id="rId4">
+          <objectPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId5">
+            <anchor moveWithCells="1" sizeWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Wordpad.Document.1" shapeId="20481" r:id="rId4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Wordpad.Document.1" shapeId="20484" r:id="rId6">
+          <objectPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId5">
+            <anchor moveWithCells="1" sizeWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Wordpad.Document.1" shapeId="20484" r:id="rId6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </oleObjects>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="20482" r:id="rId7" name="Check Box 2">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>361950</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>657225</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="20483" r:id="rId8" name="Check Box 3">
+              <controlPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>361950</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>200025</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>657225</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>200025</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8880B815-18AD-4DD9-9AF6-2D8757057938}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R24"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" customWidth="1"/>
+    <col min="2" max="2" width="81.28515625" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="58"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="75" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+    </row>
+    <row r="2" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="75"/>
+    </row>
+    <row r="3" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="57"/>
+      <c r="B3" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="57"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+    </row>
+    <row r="4" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="57"/>
+      <c r="B4" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+    </row>
+    <row r="5" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="57"/>
+      <c r="B5" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+    </row>
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L7" s="5"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="8"/>
+    </row>
+    <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="77"/>
+      <c r="I8" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="79"/>
+      <c r="K8" s="13">
+        <f>'C1 W1'!K8+7</f>
+        <v>46214</v>
+      </c>
+      <c r="L8" s="14"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="17"/>
+    </row>
+    <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="48">
+        <f t="shared" ref="G10:M10" si="0">G11</f>
+        <v>46208</v>
+      </c>
+      <c r="H10" s="48">
+        <f t="shared" si="0"/>
+        <v>46209</v>
+      </c>
+      <c r="I10" s="48">
+        <f t="shared" si="0"/>
+        <v>46210</v>
+      </c>
+      <c r="J10" s="48">
+        <f t="shared" si="0"/>
+        <v>46211</v>
+      </c>
+      <c r="K10" s="48">
+        <f t="shared" si="0"/>
+        <v>46212</v>
+      </c>
+      <c r="L10" s="48">
+        <f t="shared" si="0"/>
+        <v>46213</v>
+      </c>
+      <c r="M10" s="48">
+        <f t="shared" si="0"/>
+        <v>46214</v>
+      </c>
+      <c r="N10" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="O10" s="33"/>
+    </row>
+    <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="37"/>
+      <c r="B11" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="49">
+        <f t="shared" ref="G11:L11" si="1">H11-1</f>
+        <v>46208</v>
+      </c>
+      <c r="H11" s="49">
+        <f t="shared" si="1"/>
+        <v>46209</v>
+      </c>
+      <c r="I11" s="49">
+        <f t="shared" si="1"/>
+        <v>46210</v>
+      </c>
+      <c r="J11" s="49">
+        <f t="shared" si="1"/>
+        <v>46211</v>
+      </c>
+      <c r="K11" s="49">
+        <f t="shared" si="1"/>
+        <v>46212</v>
+      </c>
+      <c r="L11" s="49">
+        <f t="shared" si="1"/>
+        <v>46213</v>
+      </c>
+      <c r="M11" s="49">
+        <f>K8</f>
+        <v>46214</v>
+      </c>
+      <c r="N11" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="42"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+    </row>
+    <row r="13" spans="1:18" ht="0.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="54"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="55"/>
+    </row>
+    <row r="14" spans="1:18" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="47"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="69">
+        <f>SUM(G14:M14)</f>
+        <v>0</v>
+      </c>
+      <c r="R14"/>
+    </row>
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="30"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+    </row>
+    <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="40"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="41">
+        <f t="shared" ref="G16:O16" si="2">SUM(G14:G15)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="38">
+        <f>SUM(N16:O16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L18" s="24"/>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="25"/>
+      <c r="B19" s="34"/>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="26"/>
+      <c r="L19" s="73">
+        <f ca="1">NOW()</f>
+        <v>46305.419900115739</v>
+      </c>
+      <c r="M19" s="74"/>
+    </row>
+    <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L20" s="24"/>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="25"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="28"/>
+    </row>
+    <row r="22" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" s="22"/>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="28"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="M1:O4"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="L19:M19"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.14000000000000001" right="0.12" top="0.54" bottom="0.47" header="0.5" footer="0.38"/>
+  <pageSetup scale="91" orientation="landscape" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <oleObjects>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Wordpad.Document.1" shapeId="21505" r:id="rId4">
+          <objectPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId5">
+            <anchor moveWithCells="1" sizeWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Wordpad.Document.1" shapeId="21505" r:id="rId4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Wordpad.Document.1" shapeId="21508" r:id="rId6">
+          <objectPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId5">
+            <anchor moveWithCells="1" sizeWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Wordpad.Document.1" shapeId="21508" r:id="rId6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </oleObjects>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="21506" r:id="rId7" name="Check Box 2">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>361950</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>657225</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="21507" r:id="rId8" name="Check Box 3">
+              <controlPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>361950</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>200025</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>657225</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>200025</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2FA2AAA-62B2-4A83-9189-A2690C6EB3AD}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R24"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" customWidth="1"/>
+    <col min="2" max="2" width="81.28515625" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="58"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="75" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+    </row>
+    <row r="2" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="75"/>
+    </row>
+    <row r="3" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="57"/>
+      <c r="B3" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="57"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+    </row>
+    <row r="4" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="57"/>
+      <c r="B4" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+    </row>
+    <row r="5" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="57"/>
+      <c r="B5" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+    </row>
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L7" s="5"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="8"/>
+    </row>
+    <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="77"/>
+      <c r="I8" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="79"/>
+      <c r="K8" s="13">
+        <f>'C1 W1'!K8+7</f>
+        <v>46214</v>
+      </c>
+      <c r="L8" s="14"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="17"/>
+    </row>
+    <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="48">
+        <f t="shared" ref="G10:M10" si="0">G11</f>
+        <v>46208</v>
+      </c>
+      <c r="H10" s="48">
+        <f t="shared" si="0"/>
+        <v>46209</v>
+      </c>
+      <c r="I10" s="48">
+        <f t="shared" si="0"/>
+        <v>46210</v>
+      </c>
+      <c r="J10" s="48">
+        <f t="shared" si="0"/>
+        <v>46211</v>
+      </c>
+      <c r="K10" s="48">
+        <f t="shared" si="0"/>
+        <v>46212</v>
+      </c>
+      <c r="L10" s="48">
+        <f t="shared" si="0"/>
+        <v>46213</v>
+      </c>
+      <c r="M10" s="48">
+        <f t="shared" si="0"/>
+        <v>46214</v>
+      </c>
+      <c r="N10" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="O10" s="33"/>
+    </row>
+    <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="37"/>
+      <c r="B11" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="49">
+        <f t="shared" ref="G11:L11" si="1">H11-1</f>
+        <v>46208</v>
+      </c>
+      <c r="H11" s="49">
+        <f t="shared" si="1"/>
+        <v>46209</v>
+      </c>
+      <c r="I11" s="49">
+        <f t="shared" si="1"/>
+        <v>46210</v>
+      </c>
+      <c r="J11" s="49">
+        <f t="shared" si="1"/>
+        <v>46211</v>
+      </c>
+      <c r="K11" s="49">
+        <f t="shared" si="1"/>
+        <v>46212</v>
+      </c>
+      <c r="L11" s="49">
+        <f t="shared" si="1"/>
+        <v>46213</v>
+      </c>
+      <c r="M11" s="49">
+        <f>K8</f>
+        <v>46214</v>
+      </c>
+      <c r="N11" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="42"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+    </row>
+    <row r="13" spans="1:18" ht="0.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="54"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="55"/>
+    </row>
+    <row r="14" spans="1:18" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="47"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="69">
+        <f>SUM(G14:M14)</f>
+        <v>0</v>
+      </c>
+      <c r="R14"/>
+    </row>
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="30"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+    </row>
+    <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="40"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="41">
+        <f t="shared" ref="G16:O16" si="2">SUM(G14:G15)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="38">
+        <f>SUM(N16:O16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L18" s="24"/>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="25"/>
+      <c r="B19" s="34"/>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="26"/>
+      <c r="L19" s="73">
+        <f ca="1">NOW()</f>
+        <v>46305.419900115739</v>
+      </c>
+      <c r="M19" s="74"/>
+    </row>
+    <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L20" s="24"/>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="25"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="28"/>
+    </row>
+    <row r="22" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" s="22"/>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="28"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="M1:O4"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="L19:M19"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.14000000000000001" right="0.12" top="0.54" bottom="0.47" header="0.5" footer="0.38"/>
+  <pageSetup scale="91" orientation="landscape" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <oleObjects>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Wordpad.Document.1" shapeId="22529" r:id="rId4">
+          <objectPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId5">
+            <anchor moveWithCells="1" sizeWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Wordpad.Document.1" shapeId="22529" r:id="rId4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Wordpad.Document.1" shapeId="22532" r:id="rId6">
+          <objectPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId5">
+            <anchor moveWithCells="1" sizeWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Wordpad.Document.1" shapeId="22532" r:id="rId6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </oleObjects>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="22530" r:id="rId7" name="Check Box 2">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>361950</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>657225</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="22531" r:id="rId8" name="Check Box 3">
+              <controlPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>361950</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>200025</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>657225</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>200025</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28DE3AE3-E07D-48C2-9D39-B3609B70FE1E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R24"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" customWidth="1"/>
+    <col min="2" max="2" width="81.28515625" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="58"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="75" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+    </row>
+    <row r="2" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="75"/>
+    </row>
+    <row r="3" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="57"/>
+      <c r="B3" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="57"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+    </row>
+    <row r="4" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="57"/>
+      <c r="B4" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+    </row>
+    <row r="5" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="57"/>
+      <c r="B5" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+    </row>
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L7" s="5"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="8"/>
+    </row>
+    <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="77"/>
+      <c r="I8" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="79"/>
+      <c r="K8" s="13">
+        <f>'C1 W1'!K8+7</f>
+        <v>46214</v>
+      </c>
+      <c r="L8" s="14"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="17"/>
+    </row>
+    <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="48">
+        <f t="shared" ref="G10:M10" si="0">G11</f>
+        <v>46208</v>
+      </c>
+      <c r="H10" s="48">
+        <f t="shared" si="0"/>
+        <v>46209</v>
+      </c>
+      <c r="I10" s="48">
+        <f t="shared" si="0"/>
+        <v>46210</v>
+      </c>
+      <c r="J10" s="48">
+        <f t="shared" si="0"/>
+        <v>46211</v>
+      </c>
+      <c r="K10" s="48">
+        <f t="shared" si="0"/>
+        <v>46212</v>
+      </c>
+      <c r="L10" s="48">
+        <f t="shared" si="0"/>
+        <v>46213</v>
+      </c>
+      <c r="M10" s="48">
+        <f t="shared" si="0"/>
+        <v>46214</v>
+      </c>
+      <c r="N10" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="O10" s="33"/>
+    </row>
+    <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="37"/>
+      <c r="B11" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="49">
+        <f t="shared" ref="G11:L11" si="1">H11-1</f>
+        <v>46208</v>
+      </c>
+      <c r="H11" s="49">
+        <f t="shared" si="1"/>
+        <v>46209</v>
+      </c>
+      <c r="I11" s="49">
+        <f t="shared" si="1"/>
+        <v>46210</v>
+      </c>
+      <c r="J11" s="49">
+        <f t="shared" si="1"/>
+        <v>46211</v>
+      </c>
+      <c r="K11" s="49">
+        <f t="shared" si="1"/>
+        <v>46212</v>
+      </c>
+      <c r="L11" s="49">
+        <f t="shared" si="1"/>
+        <v>46213</v>
+      </c>
+      <c r="M11" s="49">
+        <f>K8</f>
+        <v>46214</v>
+      </c>
+      <c r="N11" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="42"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+    </row>
+    <row r="13" spans="1:18" ht="0.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="54"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="55"/>
+    </row>
+    <row r="14" spans="1:18" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="47"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="69">
+        <f>SUM(G14:M14)</f>
+        <v>0</v>
+      </c>
+      <c r="R14"/>
+    </row>
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="30"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+    </row>
+    <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="40"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="41">
+        <f t="shared" ref="G16:O16" si="2">SUM(G14:G15)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="38">
+        <f>SUM(N16:O16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L18" s="24"/>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="25"/>
+      <c r="B19" s="34"/>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="26"/>
+      <c r="L19" s="73">
+        <f ca="1">NOW()</f>
+        <v>46305.419900115739</v>
+      </c>
+      <c r="M19" s="74"/>
+    </row>
+    <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L20" s="24"/>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="25"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="28"/>
+    </row>
+    <row r="22" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" s="22"/>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="28"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="M1:O4"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="L19:M19"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.14000000000000001" right="0.12" top="0.54" bottom="0.47" header="0.5" footer="0.38"/>
+  <pageSetup scale="91" orientation="landscape" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <oleObjects>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Wordpad.Document.1" shapeId="23553" r:id="rId4">
+          <objectPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId5">
+            <anchor moveWithCells="1" sizeWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Wordpad.Document.1" shapeId="23553" r:id="rId4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Wordpad.Document.1" shapeId="23556" r:id="rId6">
+          <objectPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId5">
+            <anchor moveWithCells="1" sizeWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Wordpad.Document.1" shapeId="23556" r:id="rId6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </oleObjects>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="23554" r:id="rId7" name="Check Box 2">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>361950</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>657225</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="23555" r:id="rId8" name="Check Box 3">
+              <controlPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>361950</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>200025</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>657225</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>200025</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FD17DD4-2D67-466F-8D84-29ED8FDD6517}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R24"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" customWidth="1"/>
+    <col min="2" max="2" width="81.28515625" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="58"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="75" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+    </row>
+    <row r="2" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="75"/>
+    </row>
+    <row r="3" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="57"/>
+      <c r="B3" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="57"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+    </row>
+    <row r="4" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="57"/>
+      <c r="B4" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+    </row>
+    <row r="5" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="57"/>
+      <c r="B5" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+    </row>
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L7" s="5"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="8"/>
+    </row>
+    <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="77"/>
+      <c r="I8" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="79"/>
+      <c r="K8" s="13">
+        <f>'C1 W1'!K8+7</f>
+        <v>46214</v>
+      </c>
+      <c r="L8" s="14"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="17"/>
+    </row>
+    <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="48">
+        <f t="shared" ref="G10:M10" si="0">G11</f>
+        <v>46208</v>
+      </c>
+      <c r="H10" s="48">
+        <f t="shared" si="0"/>
+        <v>46209</v>
+      </c>
+      <c r="I10" s="48">
+        <f t="shared" si="0"/>
+        <v>46210</v>
+      </c>
+      <c r="J10" s="48">
+        <f t="shared" si="0"/>
+        <v>46211</v>
+      </c>
+      <c r="K10" s="48">
+        <f t="shared" si="0"/>
+        <v>46212</v>
+      </c>
+      <c r="L10" s="48">
+        <f t="shared" si="0"/>
+        <v>46213</v>
+      </c>
+      <c r="M10" s="48">
+        <f t="shared" si="0"/>
+        <v>46214</v>
+      </c>
+      <c r="N10" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="O10" s="33"/>
+    </row>
+    <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="37"/>
+      <c r="B11" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="49">
+        <f t="shared" ref="G11:L11" si="1">H11-1</f>
+        <v>46208</v>
+      </c>
+      <c r="H11" s="49">
+        <f t="shared" si="1"/>
+        <v>46209</v>
+      </c>
+      <c r="I11" s="49">
+        <f t="shared" si="1"/>
+        <v>46210</v>
+      </c>
+      <c r="J11" s="49">
+        <f t="shared" si="1"/>
+        <v>46211</v>
+      </c>
+      <c r="K11" s="49">
+        <f t="shared" si="1"/>
+        <v>46212</v>
+      </c>
+      <c r="L11" s="49">
+        <f t="shared" si="1"/>
+        <v>46213</v>
+      </c>
+      <c r="M11" s="49">
+        <f>K8</f>
+        <v>46214</v>
+      </c>
+      <c r="N11" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="42"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+    </row>
+    <row r="13" spans="1:18" ht="0.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="54"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="55"/>
+    </row>
+    <row r="14" spans="1:18" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="47"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="69">
+        <f>SUM(G14:M14)</f>
+        <v>0</v>
+      </c>
+      <c r="R14"/>
+    </row>
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="30"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+    </row>
+    <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="40"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="41">
+        <f t="shared" ref="G16:O16" si="2">SUM(G14:G15)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="38">
+        <f>SUM(N16:O16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L18" s="24"/>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="25"/>
+      <c r="B19" s="34"/>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="26"/>
+      <c r="L19" s="73">
+        <f ca="1">NOW()</f>
+        <v>46305.419900115739</v>
+      </c>
+      <c r="M19" s="74"/>
+    </row>
+    <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L20" s="24"/>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="25"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="28"/>
+    </row>
+    <row r="22" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" s="22"/>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="28"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="M1:O4"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="L19:M19"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.14000000000000001" right="0.12" top="0.54" bottom="0.47" header="0.5" footer="0.38"/>
+  <pageSetup scale="91" orientation="landscape" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <oleObjects>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Wordpad.Document.1" shapeId="24577" r:id="rId4">
+          <objectPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId5">
+            <anchor moveWithCells="1" sizeWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Wordpad.Document.1" shapeId="24577" r:id="rId4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Wordpad.Document.1" shapeId="24580" r:id="rId6">
+          <objectPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId5">
+            <anchor moveWithCells="1" sizeWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>9525</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Wordpad.Document.1" shapeId="24580" r:id="rId6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </oleObjects>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="24578" r:id="rId7" name="Check Box 2">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>361950</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>657225</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="24579" r:id="rId8" name="Check Box 3">
+              <controlPr locked="0" defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>361950</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>200025</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>12</xdr:col>
+                    <xdr:colOff>657225</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>200025</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
 </file>